--- a/Result/profitability/3093.xlsx
+++ b/Result/profitability/3093.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61</v>
+        <v>0.6125</v>
       </c>
       <c r="N2" t="n">
-        <v>33.2525</v>
+        <v>32.90375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8012499999999999</v>
+        <v>0.775</v>
       </c>
       <c r="N3" t="n">
-        <v>35.04875</v>
+        <v>33.8125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.18125</v>
+        <v>1.16875</v>
       </c>
       <c r="N4" t="n">
-        <v>37.6075</v>
+        <v>37.6925</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11125</v>
+        <v>1.125</v>
       </c>
       <c r="N5" t="n">
-        <v>39.30625000000001</v>
+        <v>39.4875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.085</v>
+        <v>1.0775</v>
       </c>
       <c r="N6" t="n">
-        <v>45.50875000000001</v>
+        <v>44.65625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03625</v>
+        <v>1.055</v>
       </c>
       <c r="N7" t="n">
-        <v>46.915</v>
+        <v>45.225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16625</v>
+        <v>1.1975</v>
       </c>
       <c r="N8" t="n">
-        <v>47.55875</v>
+        <v>47.6075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1906,7 +1906,7 @@
         <v>1.12125</v>
       </c>
       <c r="N12" t="n">
-        <v>46.98999999999999</v>
+        <v>46.99</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2033,7 +2033,7 @@
         <v>1.27</v>
       </c>
       <c r="N13" t="n">
-        <v>46.98249999999999</v>
+        <v>46.9825</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>498</v>
+      </c>
+      <c r="D75" t="n">
+        <v>362</v>
+      </c>
+      <c r="E75" t="n">
+        <v>137</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>54</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>61</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.2625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3900000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01441241685144123</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.449999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05576923076923079</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
